--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer (Job Code: 1104)</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Federal Soft Systems</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Hadoop, Hive</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,129 +601,129 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b47572932e8bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
+          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Software Engineer- Investment Research and Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
+          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Integration Architect (MuleSoft)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>Matrix Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Application Integration Architect (MuleSoft)</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Matrix Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Developer -AWS Python SQL Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, HBase, Oozie, Spark, PySpark</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690e477dea973841</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
@@ -5578,17 +5578,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Native</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>dbt Engineer</t>
+          <t>Sr. Software Engineer, AI Native</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Palmer Holland</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,24 +5911,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,32 +6096,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Experienced Solution Architect</t>
+          <t>Senior Data Engineer / Analytics Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Six Feet Up Inc.</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Windermere, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>XoriantːUS</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>XoriantːUS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>VivSoft technologies</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GCP Data Architect (Migration)</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Engineer, Site Reliability</t>
+          <t>GCP Data Architect (Migration)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72414f98b9232ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
         </is>
       </c>
     </row>
@@ -6453,17 +6453,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Shopify Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfc2fbc843f882c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Horizon Surgical Systems</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sr. Developer - Application Development JAVA N 4B</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
+          <t>SQL Server Developer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6760,41 +6760,6 @@
         </is>
       </c>
       <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>SQL Server Developer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>CloudSecurityweb</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist Engineer- Data</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a73d712d100166c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Specialist Engineer- Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecfd54adac1039</t>
+          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
         </is>
       </c>
     </row>
@@ -552,143 +552,143 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, EMR, S3, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55aa01c630cde774</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecfd54adac1039</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
+          <t>https://www.indeed.com/viewjob?jk=55aa01c630cde774</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
+          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer- Investment Research and Data</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer- Investment Research and Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Integration Architect (MuleSoft)</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Matrix Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
         </is>
       </c>
     </row>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
@@ -2521,29 +2521,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,42 +2866,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Autonomous Lab</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Autonomous Lab</t>
+          <t>Software Engineer II or III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II or III</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Req. #001109)</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer (Req. #001109)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer, AI Native</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,102 +4661,102 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Dev. Eng. III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
+          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
+          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>SQL Server Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,1757 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>MS, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>CT, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Creative Information Technology India</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Falls Church, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>American Family Insurance</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, AI Native</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DevFinOps Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>dbt Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Blue Cross of Idaho</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Meridian, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Cloud Engineer III</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Verily</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>BECU</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Palmer Holland</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Westlake, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Roadrunner</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Downers Grove, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>UI Software Developer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Telit Wireless Solutions</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Software Engineer, CRD- New Graduate</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>State Street</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Burlington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Experienced Solution Architect</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Gainwell Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Six Feet Up Inc.</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Windermere, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>XoriantːUS</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>VivSoft technologies</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>GCP Data Architect (Migration)</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Software Dev. Eng. III</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Horizon Surgical Systems</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>COLORADO SCHOOL OF MINES</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>FULLTHROTTLE</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>REGARD</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>REGARD</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>OnMed</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>White Plains, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Sr. Developer - Application Development JAVA N 4B</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>SQL Server Developer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>CloudSecurityweb</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist Engineer- Data</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, GCP, BigQuery, Dataflow</t>
+          <t>AWS, EMR, S3, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecfd54adac1039</t>
         </is>
       </c>
     </row>
@@ -552,143 +552,143 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecfd54adac1039</t>
+          <t>https://www.indeed.com/viewjob?jk=55aa01c630cde774</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55aa01c630cde774</t>
+          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
+          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Engineer- Investment Research and Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer- Investment Research and Data</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
@@ -2521,29 +2521,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,69 +2586,69 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Autonomous Lab</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GCP DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Stevens Transport</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25188e3882df38f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stevens Transport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>GCP DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=d25188e3882df38f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Senior Software Engineer (Req. #001109)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Req. #001109)</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Native</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevFinOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dbt Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer, AI Native</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Experienced Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Six Feet Up Inc.</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Windermere, FL, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VivSoft technologies</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Dev. Eng. III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
@@ -4738,17 +4738,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Horizon Surgical Systems</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Dev. Eng. III</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
+          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4870,146 +4870,6 @@
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>REGARD</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>SQL Server Developer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CloudSecurityweb</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sr. Developer - Application Development JAVA N 4B</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
         </is>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,35 +748,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2232,46 +2232,46 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,112 +2481,112 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,77 +2691,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbec198465e3aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Senior Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=a42ad39cb3a040ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,94 +2981,94 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Software Engineer II or III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,54 +3226,54 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II or III</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stevens Transport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GCP DevOps Engineer</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25188e3882df38f</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Req. #001109)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevFinOps Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dbt Engineer</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid)</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,102 +4206,102 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Native</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
@@ -4323,20 +4323,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
+          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Experienced Solution Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VivSoft technologies</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Horizon Surgical Systems</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Dev. Eng. III</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
+          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4625,251 +4625,6 @@
         </is>
       </c>
       <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>REGARD</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>REGARD</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Dev. Eng. III</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sr. Developer - Application Development JAVA N 4B</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
         </is>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,24 +2166,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2197,21 +2197,21 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
+          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
@@ -2381,29 +2381,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,104 +2411,104 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,42 +2796,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,94 +2841,94 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42ad39cb3a040ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Software Engineer II or III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II or III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevFinOps Engineer</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dbt Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,102 +3891,102 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,102 +3996,102 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Software Dev. Eng. III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,59 +4171,59 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,400 +4231,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Experienced Solution Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Gainwell Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>VivSoft technologies</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Horizon Surgical Systems</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>COLORADO SCHOOL OF MINES</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>FULLTHROTTLE</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Software Dev. Eng. III</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Sr. Developer - Application Development JAVA N 4B</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
         </is>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer- Investment Research and Data</t>
+          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer- Investment Research and Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertrandt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Consultant — System Integration &amp; MDM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
+          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2232,38 +2232,38 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
+          <t>https://www.indeed.com/viewjob?jk=61f2f9934b2c6800</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa5033561f10144</t>
         </is>
       </c>
     </row>
@@ -2311,29 +2311,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=3868dfba8a9504d2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
@@ -2381,29 +2381,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,104 +2411,104 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,42 +2796,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II or III</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, HBase, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
+          <t>https://www.indeed.com/viewjob?jk=690e477dea973841</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevFinOps Engineer</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dbt Engineer</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid)</t>
+          <t>dbt Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Senior Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,42 +3881,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VivSoft technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Horizon Surgical Systems</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,29 +4021,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
+          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-19.xlsx
+++ b/results/job_matches_2026-06-19.xlsx
@@ -573,87 +573,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
+          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89409de13fc01583</t>
+          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
+          <t>Software Engineer- Investment Research and Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer- Investment Research and Data</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Associate, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
+          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66cb4927a8da8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
         </is>
       </c>
     </row>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc61dd52578570</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960be221fd1140</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Systems Engineer - FinOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Power Automate - Contract</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer I</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51beaa63af71a055</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, HBase, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=690e477dea973841</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, HBase, Oozie, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690e477dea973841</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Associate, Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer, Applications</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid)</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,77 +3943,77 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer, CRD- New Graduate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Senior Data Warehouse Specialist/ETL Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VivSoft technologies</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,29 +4021,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist/ETL Developer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VivSoft technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90d1672fb94862c</t>
+          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Software Dev. Eng. III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08e0faf895418f5</t>
+          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Dev. Eng. III</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a2bf76319d1fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>
